--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.87168490296738</v>
+        <v>5.829148796732199</v>
       </c>
       <c r="D2" t="n">
-        <v>5.100356157517712</v>
+        <v>0.8288078755966283</v>
       </c>
       <c r="E2" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F2" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.71201750581744</v>
+        <v>9.540702844695335</v>
       </c>
       <c r="D3" t="n">
-        <v>23.98247697816452</v>
+        <v>3.897152508951735</v>
       </c>
       <c r="E3" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F3" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.61422194293091</v>
+        <v>8.549811065726272</v>
       </c>
       <c r="D4" t="n">
-        <v>17.11568164958762</v>
+        <v>2.781298268057989</v>
       </c>
       <c r="E4" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F4" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.70010583871876</v>
+        <v>8.563767198791798</v>
       </c>
       <c r="D5" t="n">
-        <v>17.65240714096127</v>
+        <v>2.868516160406207</v>
       </c>
       <c r="E5" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F5" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.48549716923481</v>
+        <v>2.191393290000657</v>
       </c>
       <c r="D6" t="n">
-        <v>27.27344992397595</v>
+        <v>4.431935612646092</v>
       </c>
       <c r="E6" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F6" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.80226579018906</v>
+        <v>4.680368190905722</v>
       </c>
       <c r="D7" t="n">
-        <v>15.42670580008588</v>
+        <v>2.506839692513956</v>
       </c>
       <c r="E7" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F7" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.67271416895012</v>
+        <v>3.359316052454395</v>
       </c>
       <c r="D8" t="n">
-        <v>42.28312042520864</v>
+        <v>6.871007069096405</v>
       </c>
       <c r="E8" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F8" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>3.907273342993478</v>
+        <v>0.6349319182364401</v>
       </c>
       <c r="D9" t="n">
-        <v>11.55337113809762</v>
+        <v>1.877422809940864</v>
       </c>
       <c r="E9" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F9" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.10298521114399</v>
+        <v>4.566735096810898</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31695784882083</v>
+        <v>5.414005650433386</v>
       </c>
       <c r="E10" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F10" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.44346007778755</v>
+        <v>3.159562262640477</v>
       </c>
       <c r="D11" t="n">
-        <v>6.22953277669653</v>
+        <v>1.012299076213186</v>
       </c>
       <c r="E11" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F11" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.36617891317053</v>
+        <v>4.934504073390212</v>
       </c>
       <c r="D12" t="n">
-        <v>17.12330743115651</v>
+        <v>2.782537457562933</v>
       </c>
       <c r="E12" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F12" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.56562995822052</v>
+        <v>2.691914868210835</v>
       </c>
       <c r="D13" t="n">
-        <v>9.342424187818278</v>
+        <v>1.51814393052047</v>
       </c>
       <c r="E13" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F13" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.28025942047176</v>
+        <v>6.545542155826662</v>
       </c>
       <c r="D14" t="n">
-        <v>23.65797113295647</v>
+        <v>3.844420309105426</v>
       </c>
       <c r="E14" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F14" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.30261627002122</v>
+        <v>4.274175143878448</v>
       </c>
       <c r="D15" t="n">
-        <v>4.551189654063514</v>
+        <v>0.7395683187853211</v>
       </c>
       <c r="E15" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F15" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.08349091448064</v>
+        <v>6.676067273603104</v>
       </c>
       <c r="D16" t="n">
-        <v>12.1844044654493</v>
+        <v>1.979965725635512</v>
       </c>
       <c r="E16" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F16" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.2163134510276</v>
+        <v>5.397650935791986</v>
       </c>
       <c r="D17" t="n">
-        <v>2.243022001123083</v>
+        <v>0.364491075182501</v>
       </c>
       <c r="E17" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F17" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>69.50981996622262</v>
+        <v>11.29534574451118</v>
       </c>
       <c r="D18" t="n">
-        <v>40.10502328920838</v>
+        <v>6.517066284496361</v>
       </c>
       <c r="E18" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F18" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>64.77748550078796</v>
+        <v>10.52634139387804</v>
       </c>
       <c r="D19" t="n">
-        <v>31.23400098026501</v>
+        <v>5.075525159293064</v>
       </c>
       <c r="E19" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F19" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>62.71468749814852</v>
+        <v>10.19113671844914</v>
       </c>
       <c r="D20" t="n">
-        <v>28.28353386117506</v>
+        <v>4.596074252440947</v>
       </c>
       <c r="E20" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F20" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>91.46002280854118</v>
+        <v>14.86225370638794</v>
       </c>
       <c r="D21" t="n">
-        <v>64.00563238939057</v>
+        <v>10.40091526327597</v>
       </c>
       <c r="E21" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F21" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>75.84476573969239</v>
+        <v>12.32477443270001</v>
       </c>
       <c r="D22" t="n">
-        <v>42.28505107267001</v>
+        <v>6.871320799308877</v>
       </c>
       <c r="E22" t="n">
-        <v>22.39645935462701</v>
+        <v>3.639424645126889</v>
       </c>
       <c r="F22" t="n">
-        <v>15.27373220339562</v>
+        <v>2.481981483051789</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
